--- a/benchmark/generated_files/CC-2_M_004.xlsx
+++ b/benchmark/generated_files/CC-2_M_004.xlsx
@@ -433,28 +433,21 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>IBAN: IT28 W030 6909 6061 0000 0075 849</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Codice cliente: 207241</t>
+          <t>Intestatario: Marco Rossi (P.IVA)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Filiale: SEDE CENTRALE</t>
+          <t>Movimenti al 28/02/2026</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Intestatario: Marco Rossi (P.IVA)</t>
+          <t>Saldo iniziale: 23.726,98 EUR</t>
         </is>
       </c>
     </row>
@@ -465,13 +458,6 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Banca: Banca Sella</t>
-        </is>
-      </c>
-    </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
@@ -479,10 +465,10 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Movimenti al 28/02/2026</t>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>IBAN: IT28 W030 6909 6061 0000 0075 849</t>
         </is>
       </c>
     </row>
@@ -587,15 +573,15 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>46027</v>
+        <v>46025</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:211821504 ORD. DELTA SOLUTIONS SPA</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>2419.26</v>
+          <t>Bonif. v/fav. - RIF:215455972 ORD. ROSSI MARCO GIROCONTO</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>902.26</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -605,15 +591,15 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>46029</v>
+        <v>46027</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:216055937 ORD. GAMMA TECHNOLOGIES SRL</t>
+          <t>Bonif. v/fav. - RIF:211821504 ORD. DELTA SOLUTIONS SPA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3299.42</v>
+        <v>2419.26</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -623,15 +609,15 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>46031</v>
+        <v>46029</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:214528994 ORD. BETA CONSULTING SRL</t>
+          <t>Bonif. v/fav. - RIF:216055937 ORD. GAMMA TECHNOLOGIES SRL</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>5417.09</v>
+        <v>3299.42</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -641,15 +627,15 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>46032</v>
+        <v>46031</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:210678132 ORD. DELTA SOLUTIONS SPA</t>
+          <t>Bonif. v/fav. - RIF:214528994 ORD. BETA CONSULTING SRL</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>4443.68</v>
+        <v>5417.09</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -663,11 +649,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:213864570 ORD. GAMMA TECHNOLOGIES SRL</t>
+          <t>Bonif. v/fav. - RIF:210678132 ORD. DELTA SOLUTIONS SPA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2247.62</v>
+        <v>4443.68</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -677,15 +663,15 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>46035</v>
+        <v>46032</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>RICARICA HYPE DA CONTO 0075849</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>54.85</v>
+          <t>Bonif. v/fav. - RIF:213864570 ORD. GAMMA TECHNOLOGIES SRL</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>2247.62</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -699,11 +685,11 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:214088109 ORD. DELTA SOLUTIONS SPA</t>
+          <t>Bonif. v/fav. - RIF:219117902 ORD. EPSILON DIGITAL SRL</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>3863.16</v>
+        <v>5125.21</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -713,15 +699,15 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>46037</v>
+        <v>46036</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:213598010 ORD. BETA CONSULTING SRL</t>
+          <t>Bonif. v/fav. - RIF:214088109 ORD. DELTA SOLUTIONS SPA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>3286.38</v>
+        <v>3863.16</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -735,11 +721,11 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>RICARICA HYPE DA CONTO 0075849</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>69.8</v>
+          <t>Bonif. v/fav. - RIF:213598010 ORD. BETA CONSULTING SRL</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>3286.38</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -753,11 +739,11 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:211789949 ORD. GAMMA TECHNOLOGIES SRL</t>
+          <t>Bonif. v/fav. - RIF:218625782 ORD. EPSILON DIGITAL SRL</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>4845.34</v>
+        <v>4891.93</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -767,15 +753,15 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>46039</v>
+        <v>46038</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:219372268 ORD. EPSILON DIGITAL SRL</t>
+          <t>Bonif. v/fav. - RIF:211789949 ORD. GAMMA TECHNOLOGIES SRL</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>2200.14</v>
+        <v>4845.34</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -785,15 +771,15 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>46040</v>
+        <v>46039</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Addebito SDD - TELEPASS S.P.A. PEDAGGI</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>80.41</v>
+          <t>Bonif. v/fav. - RIF:219372268 ORD. EPSILON DIGITAL SRL</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>2200.14</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -803,15 +789,15 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>46041</v>
+        <v>46044</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>GIROCONTO DA CC 0075849 A CC 0123456</t>
+          <t>Pagam. POS - PAGAMENTO POS 155,71 EUR DEL 22.01.2026 A (ITA) MEDIAWORLD CARUGATE</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>745.8200000000001</v>
+        <v>155.71</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -875,15 +861,15 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>46046</v>
+        <v>46045</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:216721705 ORD. CLIENTE ALFA S.P.A.</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>1820.16</v>
+          <t>Bonif. v/fav. - RIF:210139537 ORD. ROSSI MARCO GIROCONTO</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>628.4400000000001</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -893,15 +879,15 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>46047</v>
+        <v>46046</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:214357055 ORD. GAMMA TECHNOLOGIES SRL</t>
+          <t>Bonif. v/fav. - RIF:216721705 ORD. CLIENTE ALFA S.P.A.</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>3824.03</v>
+        <v>1820.16</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -911,15 +897,15 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>46049</v>
+        <v>46047</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:212739207 ORD. ROSSI MARCO GIROCONTO</t>
-        </is>
-      </c>
-      <c r="C34" t="n">
-        <v>576.33</v>
+          <t>Bonif. v/fav. - RIF:214357055 ORD. GAMMA TECHNOLOGIES SRL</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>3824.03</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -929,15 +915,15 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>46053</v>
+        <v>46049</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:212331501 ORD. CLIENTE ALFA S.P.A.</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>5048.69</v>
+          <t>RICARICA HYPE DA CONTO 0075849</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>88.93000000000001</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -951,11 +937,11 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:219882586 ORD. DELTA SOLUTIONS SPA</t>
+          <t>Bonif. v/fav. - RIF:212331501 ORD. CLIENTE ALFA S.P.A.</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>4658.22</v>
+        <v>5048.69</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -969,11 +955,11 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:214257682 ORD. EPSILON DIGITAL SRL</t>
+          <t>Bonif. v/fav. - RIF:219882586 ORD. DELTA SOLUTIONS SPA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>2214.88</v>
+        <v>4658.22</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -987,11 +973,11 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:218790972 ORD. CLIENTE ALFA S.P.A.</t>
+          <t>Bonif. v/fav. - RIF:214257682 ORD. EPSILON DIGITAL SRL</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>3693.73</v>
+        <v>2214.88</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -1001,15 +987,15 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>46055</v>
+        <v>46053</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:218625782 ORD. BETA CONSULTING SRL</t>
+          <t>Bonif. v/fav. - RIF:218790972 ORD. CLIENTE ALFA S.P.A.</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1542.37</v>
+        <v>3693.73</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -1019,15 +1005,15 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>46056</v>
+        <v>46053</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:219707824 ORD. GAMMA TECHNOLOGIES SRL</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>4034.27</v>
+          <t>RICARICA HYPE DA CONTO 0075849</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>251.18</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -1037,15 +1023,15 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>46057</v>
+        <v>46056</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:217057906 ORD. DELTA SOLUTIONS SPA</t>
+          <t>Bonif. v/fav. - RIF:219707824 ORD. GAMMA TECHNOLOGIES SRL</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>4810.09</v>
+        <v>4034.27</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -1055,15 +1041,15 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>46060</v>
+        <v>46057</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:218782198 ORD. EPSILON DIGITAL SRL</t>
+          <t>Bonif. v/fav. - RIF:217057906 ORD. DELTA SOLUTIONS SPA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>3890.34</v>
+        <v>4810.09</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -1073,15 +1059,15 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>46061</v>
+        <v>46059</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:218569884 ORD. EPSILON DIGITAL SRL</t>
-        </is>
-      </c>
-      <c r="D43" t="n">
-        <v>2070.85</v>
+          <t>Pagam. POS - PAGAMENTO POS 73,18 EUR DEL 06.02.2026 A (ITA) ROSTICCERIA DA MARIO</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>73.18000000000001</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -1095,11 +1081,11 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:218915915 ORD. DELTA SOLUTIONS SPA</t>
+          <t>Bonif. v/fav. - RIF:218569884 ORD. EPSILON DIGITAL SRL</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>1885.19</v>
+        <v>2070.85</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -1113,11 +1099,11 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:210605005 ORD. BETA CONSULTING SRL</t>
+          <t>Bonif. v/fav. - RIF:218915915 ORD. DELTA SOLUTIONS SPA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>3542.19</v>
+        <v>1885.19</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -1127,15 +1113,15 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>46064</v>
+        <v>46061</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Addebito SDD - JETBRAINS S.R.O. INTELLIJ IDEA</t>
-        </is>
-      </c>
-      <c r="C46" t="n">
-        <v>189.86</v>
+          <t>Bonif. v/fav. - RIF:210605005 ORD. BETA CONSULTING SRL</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>3542.19</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -1145,15 +1131,15 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>46064</v>
+        <v>46063</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:214220919 ORD. CLIENTE ALFA S.P.A.</t>
-        </is>
-      </c>
-      <c r="D47" t="n">
-        <v>5092.91</v>
+          <t>RICARICA HYPE DA CONTO 0075849</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>180.86</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -1167,11 +1153,11 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>RICARICA HYPE DA CONTO 0075849</t>
-        </is>
-      </c>
-      <c r="C48" t="n">
-        <v>153.23</v>
+          <t>Bonif. v/fav. - RIF:214220919 ORD. CLIENTE ALFA S.P.A.</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>5092.91</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -1185,11 +1171,11 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:217879825 ORD. GAMMA TECHNOLOGIES SRL</t>
-        </is>
-      </c>
-      <c r="D49" t="n">
-        <v>2327.1</v>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 3762 BUREAU VALLÉE</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>105.59</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -1203,11 +1189,11 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:217838205 ORD. GAMMA TECHNOLOGIES SRL</t>
+          <t>Bonif. v/fav. - RIF:217879825 ORD. GAMMA TECHNOLOGIES SRL</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>2927.36</v>
+        <v>2327.1</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -1289,15 +1275,15 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>46070</v>
+        <v>46069</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:217071943 ORD. CLIENTE ALFA S.P.A.</t>
+          <t>Bonif. v/fav. - RIF:210312564 ORD. CLIENTE ALFA S.P.A.</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>2098.19</v>
+        <v>5045.34</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -1307,15 +1293,15 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>46071</v>
+        <v>46070</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:213726098 ORD. GAMMA TECHNOLOGIES SRL</t>
+          <t>Bonif. v/fav. - RIF:217071943 ORD. CLIENTE ALFA S.P.A.</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>5164.03</v>
+        <v>2098.19</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -1325,15 +1311,15 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>46072</v>
+        <v>46071</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Addebito SDD - SPOTIFY AB</t>
-        </is>
-      </c>
-      <c r="C57" t="n">
-        <v>76.48</v>
+          <t>Bonif. v/fav. - RIF:213726098 ORD. GAMMA TECHNOLOGIES SRL</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>5164.03</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -1347,11 +1333,11 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:219832793 ORD. REGIONE LOMBARDIA BONUS</t>
+          <t>Bonif. v/fav. - RIF:212948933 ORD. EPSILON DIGITAL SRL</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>229.75</v>
+        <v>2721.89</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -1361,15 +1347,15 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>46073</v>
+        <v>46072</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:216684074 ORD. GAMMA TECHNOLOGIES SRL</t>
+          <t>Bonif. v/fav. - RIF:217796391 ORD. GAMMA TECHNOLOGIES SRL</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>3446.48</v>
+        <v>3858.4</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -1379,15 +1365,15 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>46074</v>
+        <v>46072</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:218986747 ORD. GAMMA TECHNOLOGIES SRL</t>
+          <t>Bonif. v/fav. - RIF:219832793 ORD. REGIONE LOMBARDIA BONUS</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>2762.92</v>
+        <v>229.75</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -1397,15 +1383,15 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>46074</v>
+        <v>46073</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:216915632 ORD. GAMMA TECHNOLOGIES SRL</t>
-        </is>
-      </c>
-      <c r="D61" t="n">
-        <v>1858.22</v>
+          <t>Disposizione - RIF:216031174 BEN. STUDIO COMM.LE FERRI &amp; ASSOCIATI</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>82.03</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -1415,15 +1401,15 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>46074</v>
+        <v>46073</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>RICARICA HYPE DA CONTO 0075849</t>
-        </is>
-      </c>
-      <c r="C62" t="n">
-        <v>199.25</v>
+          <t>Bonif. v/fav. - RIF:216684074 ORD. GAMMA TECHNOLOGIES SRL</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>3446.48</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -1433,15 +1419,15 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>46075</v>
+        <v>46074</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:210179690 ORD. REGIONE LOMBARDIA BONUS</t>
+          <t>Bonif. v/fav. - RIF:218986747 ORD. GAMMA TECHNOLOGIES SRL</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>128.87</v>
+        <v>2762.92</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -1455,11 +1441,11 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:217995273 ORD. EPSILON DIGITAL SRL</t>
+          <t>Bonif. v/fav. - RIF:210179690 ORD. REGIONE LOMBARDIA BONUS</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>2867.97</v>
+        <v>128.87</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -1469,15 +1455,15 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>46076</v>
+        <v>46075</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:215829664 ORD. EPSILON DIGITAL SRL</t>
+          <t>Bonif. v/fav. - RIF:217995273 ORD. EPSILON DIGITAL SRL</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>3736.46</v>
+        <v>2867.97</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -1487,15 +1473,15 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>46077</v>
+        <v>46076</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Addebito SDD - BANCA INTESA SANPAOLO MUTUO RAT. 219899166</t>
-        </is>
-      </c>
-      <c r="C66" t="n">
-        <v>108.54</v>
+          <t>Bonif. v/fav. - RIF:215829664 ORD. EPSILON DIGITAL SRL</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>3736.46</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -1541,15 +1527,15 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:218977469 ORD. GAMMA TECHNOLOGIES SRL</t>
-        </is>
-      </c>
-      <c r="D69" t="n">
-        <v>2045.2</v>
+          <t>RICARICA HYPE DA CONTO 0075849</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>187.14</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -1650,7 +1636,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Saldo finale: 24.084,14 EUR</t>
+          <t>Saldo finale: 21.590,67 EUR</t>
         </is>
       </c>
     </row>
